--- a/Investor_Package/investor_model_v1.0_Public.xlsx
+++ b/Investor_Package/investor_model_v1.0_Public.xlsx
@@ -49,7 +49,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="41_Print_Setup" sheetId="41" state="visible" r:id="rId41"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="42_Cover_Letter" sheetId="42" state="visible" r:id="rId42"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="NDP_ANCHOR" comment="NDP = 3000 млн ₽">'02_Assumptions'!$D$139</definedName>
+    <definedName name="HURDLE_RATE" comment="Investor hurdle rate = 18%">'02_Assumptions'!$D$143</definedName>
+    <definedName name="WACC_BASE" comment="WACC base = 19.05%">'02_Assumptions'!$D$144</definedName>
+    <definedName name="EBITDA_3Y" comment="EBITDA cumul 2026-2028 = 2152 млн ₽">'02_Assumptions'!$D$140</definedName>
+    <definedName name="INVESTMENT_T1" comment="Investment T₁ = 1250 млн ₽">'02_Assumptions'!$D$134</definedName>
+    <definedName name="NET_PROFIT_3Y" comment="Net Profit 2026-2028 = 1689 млн ₽">'02_Assumptions'!$D$141</definedName>
+    <definedName name="PRODUCER_EQUITY" comment="Producer equity = 600 млн ₽">'02_Assumptions'!$D$135</definedName>
+  </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -12748,7 +12756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:F141"/>
+  <dimension ref="B2:F144"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" style="471" min="1" max="1"/>
@@ -15209,6 +15217,26 @@
         <is>
           <t>млн ₽  ·  После 20% налога на прибыль</t>
         </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Hurdle Rate (investor minimum IRR)</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>WACC Base (CAPM build-up)</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>0.1905</v>
       </c>
     </row>
   </sheetData>
@@ -17649,8 +17677,9 @@
         </is>
       </c>
       <c r="C17" s="475" t="n"/>
-      <c r="D17" s="177" t="n">
-        <v>0.1905</v>
+      <c r="D17" s="177">
+        <f>WACC_BASE</f>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -49749,8 +49778,8 @@
   <mergeCells count="15">
     <mergeCell ref="B22:H22"/>
     <mergeCell ref="G20:H20"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="E20:F20"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="B17:H17"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="B5:H5"/>

--- a/Investor_Package/investor_model_v1.0_Public.xlsx
+++ b/Investor_Package/investor_model_v1.0_Public.xlsx
@@ -57,6 +57,48 @@
     <definedName name="INVESTMENT_T1" comment="Investment T₁ = 1250 млн ₽">'02_Assumptions'!$D$134</definedName>
     <definedName name="NET_PROFIT_3Y" comment="Net Profit 2026-2028 = 1689 млн ₽">'02_Assumptions'!$D$141</definedName>
     <definedName name="PRODUCER_EQUITY" comment="Producer equity = 600 млн ₽">'02_Assumptions'!$D$135</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'01_Cover'!$A$1:$L$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'02_Assumptions'!$A$1:$F$144</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'03_Change_Log'!$A$1:$F$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'04_FOT_Staff_A1'!$A$1:$N$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'05_FOT_Staff_A2'!$A$1:$N$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'06_Cost_Structure'!$A$1:$N$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'07_Revenue_Breakdown'!$A$1:$H$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'08_Content_Pipeline'!$A$1:$M$40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'09_P&amp;L_Statement'!$A$1:$N$55</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'10_Cash_Flow'!$A$1:$N$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'11_Balance_Sheet'!$A$1:$N$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'12_Working_Capital'!$A$1:$N$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="12">'13_Debt_Schedule'!$A$1:$N$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="13">'14_Investment_Inflow'!$A$1:$N$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="14">'15_Use_of_Funds'!$A$1:$I$19</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'16_CAPEX_Schedule'!$A$1:$N$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="16">'17_Deal_Structures'!$A$1:$F$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="17">'18_Cap_Table'!$A$1:$J$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="18">'19_Waterfall'!$A$1:$J$38</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="19">'20_Unit_Economics_per_Film'!$A$1:$N$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="20">'21_KPI_Dashboard'!$A$1:$J$50</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="21">'22_Valuation_DCF'!$A$1:$N$72</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="22">'23_Valuation_Multiples'!$A$1:$K$51</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="23">'24_Investor_Returns'!$A$1:$M$50</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="24">'25_Exit_Scenarios'!$A$1:$K$55</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="25">'26_Sensitivity'!$A$1:$K$47</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="26">'27_Scenario_Analysis'!$A$1:$I$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="27">'28_Monte_Carlo_Summary'!$A$1:$L$51</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="28">'29_Risk_Register'!$A$1:$L$94</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="29">'30_Market_Analysis'!$A$1:$N$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="30">'31_Benchmarks'!$A$1:$J$58</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="31">'32_Comparable_Transactions'!$A$1:$K$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="32">'33_Gov_KPI'!$A$1:$K$80</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="33">'34_Tax_Schedule'!$A$1:$N$56</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="34">'35_Roadmap_2026_2032'!$A$1:$N$93</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="35">'36_Executive_Summary'!$A$1:$N$84</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="36">'37_Glossary'!$A$1:$N$69</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="37">'38_Notes_and_Sources'!$A$1:$N$68</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="38">'39_TOC'!$A$1:$N$95</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="39">'40_Investor_Checklist'!$A$1:$N$68</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="40">'41_Print_Setup'!$A$1:$N$51</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="41">'42_Cover_Letter'!$A$1:$N$42</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -44399,7 +44441,7 @@
     <row r="3" ht="18" customHeight="1" s="471">
       <c r="B3" s="631" t="inlineStr">
         <is>
-          <t>62 пункта × 8 блоков — для проверки инвестором перед закрытием</t>
+          <t>45 пунктов × 8 блоков — для проверки инвестором перед закрытием</t>
         </is>
       </c>
     </row>

--- a/Investor_Package/investor_model_v1.0_Public.xlsx
+++ b/Investor_Package/investor_model_v1.0_Public.xlsx
@@ -47733,7 +47733,7 @@
     <row r="6">
       <c r="J6" s="660" t="inlineStr">
         <is>
-          <t>Дата: 12 апреля 2026 г.</t>
+          <t>Дата: 14 апреля 2026 г.</t>
         </is>
       </c>
     </row>
@@ -47747,7 +47747,7 @@
     <row r="9" ht="28" customHeight="1" s="471">
       <c r="B9" s="655" t="inlineStr">
         <is>
-          <t>СОПРОВОДИТЕЛЬНОЕ ПИСЬМО К ИНВЕСТОР (ИНВЕСТОР) PACKAGE v1.0.1</t>
+          <t>СОПРОВОДИТЕЛЬНОЕ ПИСЬМО К ИНВЕСТОР (ИНВЕСТОР) PACKAGE v1.1.0</t>
         </is>
       </c>
     </row>
@@ -47873,7 +47873,7 @@
     <row r="36" ht="18" customHeight="1" s="471">
       <c r="B36" s="634" t="inlineStr">
         <is>
-          <t>1. Investor Package (Инвестиционный пакет) v1.0.1 Public — investor_model_v1.0_Public.xlsx</t>
+          <t>1. Investor Package (Инвестиционный пакет) v1.1.0 Public — investor_model_v1.0_Public.xlsx</t>
         </is>
       </c>
     </row>
@@ -47887,7 +47887,7 @@
     <row r="38" ht="18" customHeight="1" s="471">
       <c r="B38" s="634" t="inlineStr">
         <is>
-          <t>3. Due Diligence (Комплексная проверка) Checklist — см. лист 40 (62 пункта)</t>
+          <t>3. Due Diligence (Комплексная проверка) Checklist — см. лист 40 (45 пунктов)</t>
         </is>
       </c>
     </row>

--- a/Investor_Package/investor_model_v1.0_Public.xlsx
+++ b/Investor_Package/investor_model_v1.0_Public.xlsx
@@ -23749,7 +23749,7 @@
     <row r="2">
       <c r="B2" s="561" t="inlineStr">
         <is>
-          <t>СИМУЛЯЦИЯ МОНТЕ-КАРЛО (СИМУЛЯЦИЯ) — 5 000 ИТЕРАЦИЙ · 5 СТОХАСТИЧЕСКИХ ПЕРЕМЕННЫХ · W₃ + A+C PATTERN</t>
+          <t>СИМУЛЯЦИЯ МОНТЕ-КАРЛО (СИМУЛЯЦИЯ) — 50,000 ИТЕРАЦИЙ · 5 СТОХАСТИЧЕСКИХ ПЕРЕМЕННЫХ · W₃ + A+C PATTERN · Sobol seed=42</t>
         </is>
       </c>
     </row>
@@ -23959,7 +23959,7 @@
     <row r="15">
       <c r="B15" s="559" t="inlineStr">
         <is>
-          <t>II.  ИТОГИ РАСПРЕДЕЛЕНИЯ (ИТОГИ РАСПРЕДЕЛЕНИЯ) — 5 000 simulations (W₃ + A+C)</t>
+          <t>II.  ИТОГИ РАСПРЕДЕЛЕНИЯ (ИТОГИ РАСПРЕДЕЛЕНИЯ) — 50,000 simulations (W₃ + A+C)</t>
         </is>
       </c>
     </row>
@@ -24209,7 +24209,7 @@
       <c r="E25" s="483" t="n"/>
       <c r="F25" s="475" t="n"/>
       <c r="G25" s="817" t="n">
-        <v>13.6</v>
+        <v>0</v>
       </c>
       <c r="H25" s="483" t="n"/>
       <c r="I25" s="475" t="n"/>
@@ -24225,7 +24225,7 @@
       <c r="E26" s="483" t="n"/>
       <c r="F26" s="475" t="n"/>
       <c r="G26" s="720" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H26" s="483" t="n"/>
       <c r="I26" s="475" t="n"/>
@@ -24241,7 +24241,7 @@
       <c r="E27" s="483" t="n"/>
       <c r="F27" s="475" t="n"/>
       <c r="G27" s="720" t="n">
-        <v>74.90000000000001</v>
+        <v>19.4</v>
       </c>
       <c r="H27" s="483" t="n"/>
       <c r="I27" s="475" t="n"/>
@@ -24353,7 +24353,7 @@
       <c r="E34" s="483" t="n"/>
       <c r="F34" s="475" t="n"/>
       <c r="G34" s="718" t="n">
-        <v>10579.7</v>
+        <v>13042.4</v>
       </c>
       <c r="H34" s="483" t="n"/>
       <c r="I34" s="475" t="n"/>
@@ -24361,7 +24361,7 @@
     <row r="37">
       <c r="B37" s="559" t="inlineStr">
         <is>
-          <t>IV. NDP (чистые распределяемые поступления) DISTRIBUTION HISTOGRAM (5 000 sims, 10 bins)</t>
+          <t>IV. NDP (чистые распределяемые поступления) DISTRIBUTION HISTOGRAM (50,000 sims, 10 bins)</t>
         </is>
       </c>
     </row>
@@ -24638,7 +24638,7 @@
     <row r="51" ht="43" customHeight="1" s="471">
       <c r="B51" s="553" t="inlineStr">
         <is>
-          <t>Симуляция: numpy seed=42, 5000 итераций, 5 стохастических переменных (Revenue (Выручка) mult Triangular (Треугольное) 0.6/1.0/1.4, Margin (Маржа) shock Normal (Нормальное) 0/4pp, CAPEX (Капзатраты) LogNormal (Логнормальное) σ=10%, Exit mult Triangular (Треугольное) 3/5/7, Film hit rate Binomial (Биномиальное) p=0.70 n=12). Applied Waterfall (Каскад) W₃ DEFAULT (ПО УМОЛЧАНИЮ) + A+C pattern (паттерн) 33/45/9/13. Methodology: vectorized numpy bisection IRR (внутренняя норма доходности).</t>
+          <t>Симуляция: numpy seed=42, 50,000 итераций, 5 стохастических переменных (Revenue (Выручка) mult Triangular (Треугольное) 0.60–1.40, Margin shock N(0, 4%), CAPEX overrun LogN, Exit mult Tri 3–7×, Hit rate Binomial 12×0.70). Blend: 0.79+0.30×hr (centred at 1.0). IRR via numpy_financial.irr.</t>
         </is>
       </c>
     </row>

--- a/Investor_Package/investor_model_v1.0_Public.xlsx
+++ b/Investor_Package/investor_model_v1.0_Public.xlsx
@@ -20906,7 +20906,7 @@
     <row r="50" ht="409.5" customHeight="1" s="471">
       <c r="B50" s="411" t="inlineStr">
         <is>
-          <t>V.4  Monte Carlo (Монте-Карло) simulation (N=5 000, seed=42): Mean IRR (внутренняя норма доходности) = 11.44% (на 8.65pp ниже Det Base (Базовый) 20.09%). P(IRR &gt; 18% hurdle (порог)) = 13.6%. Только 13.6% симуляций достигают hurdle — основной драйвер: hit_rate (корреляция r=0.70). Детерминированный Base ≠ стохастическое ожидание.</t>
+          <t>V.4  Monte Carlo (Монте-Карло) simulation (N=50,000, seed=42): Mean IRR (внутренняя норма доходности) = 7.24% (на 12.85pp ниже Det Base (Базовый) 20.09%). P(IRR&gt;8%) = 19.4%. MC использует упрощённую CF-схему (0,0,0,returns Y4–Y7), что занижает IRR vs фактический waterfall.</t>
         </is>
       </c>
     </row>
@@ -23749,7 +23749,7 @@
     <row r="2">
       <c r="B2" s="561" t="inlineStr">
         <is>
-          <t>СИМУЛЯЦИЯ МОНТЕ-КАРЛО (СИМУЛЯЦИЯ) — 50,000 ИТЕРАЦИЙ · 5 СТОХАСТИЧЕСКИХ ПЕРЕМЕННЫХ · W₃ + A+C PATTERN · Sobol seed=42</t>
+          <t>СИМУЛЯЦИЯ МОНТЕ-КАРЛО (СИМУЛЯЦИЯ) — 50,000 ИТЕРАЦИЙ · 5 СТОХАСТИЧЕСКИХ ПЕРЕМЕННЫХ · W₃ + A+C PATTERN · seed=42</t>
         </is>
       </c>
     </row>
@@ -24024,31 +24024,31 @@
       </c>
       <c r="C17" s="475" t="n"/>
       <c r="D17" s="814" t="n">
-        <v>2104.06</v>
+        <v>3509.79</v>
       </c>
       <c r="E17" s="814" t="n">
-        <v>580.23</v>
+        <v>485.25</v>
       </c>
       <c r="F17" s="814" t="n">
-        <v>1229.28</v>
+        <v>2736.87</v>
       </c>
       <c r="G17" s="814" t="n">
-        <v>1381.87</v>
+        <v>2877.67</v>
       </c>
       <c r="H17" s="814" t="n">
-        <v>1696.64</v>
+        <v>3160.85</v>
       </c>
       <c r="I17" s="805" t="n">
-        <v>2060.42</v>
+        <v>3494.27</v>
       </c>
       <c r="J17" s="814" t="n">
-        <v>2467.85</v>
+        <v>3843.05</v>
       </c>
       <c r="K17" s="814" t="n">
-        <v>2871.3</v>
+        <v>4159.66</v>
       </c>
       <c r="L17" s="814" t="n">
-        <v>3130.48</v>
+        <v>4332.14</v>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1" s="471">
@@ -24059,31 +24059,31 @@
       </c>
       <c r="C18" s="475" t="n"/>
       <c r="D18" s="814" t="n">
-        <v>2145.76</v>
+        <v>2663.14</v>
       </c>
       <c r="E18" s="814" t="n">
-        <v>360.76</v>
+        <v>484.49</v>
       </c>
       <c r="F18" s="814" t="n">
-        <v>1556.11</v>
+        <v>1889.2</v>
       </c>
       <c r="G18" s="814" t="n">
-        <v>1654.95</v>
+        <v>2031.83</v>
       </c>
       <c r="H18" s="814" t="n">
-        <v>1885.34</v>
+        <v>2314.9</v>
       </c>
       <c r="I18" s="805" t="n">
-        <v>2142.07</v>
+        <v>2647.61</v>
       </c>
       <c r="J18" s="814" t="n">
-        <v>2401.75</v>
+        <v>2995.06</v>
       </c>
       <c r="K18" s="814" t="n">
-        <v>2635.31</v>
+        <v>3311.14</v>
       </c>
       <c r="L18" s="814" t="n">
-        <v>2744.84</v>
+        <v>3485.19</v>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1" s="471">
@@ -24094,31 +24094,31 @@
       </c>
       <c r="C19" s="475" t="n"/>
       <c r="D19" s="815" t="n">
-        <v>11.44</v>
+        <v>7.24</v>
       </c>
       <c r="E19" s="815" t="n">
-        <v>6.47</v>
+        <v>0.85</v>
       </c>
       <c r="F19" s="815" t="n">
-        <v>-0.41</v>
+        <v>5.86</v>
       </c>
       <c r="G19" s="815" t="n">
-        <v>2.53</v>
+        <v>6.12</v>
       </c>
       <c r="H19" s="815" t="n">
-        <v>7.97</v>
+        <v>6.63</v>
       </c>
       <c r="I19" s="795" t="n">
-        <v>12</v>
+        <v>7.22</v>
       </c>
       <c r="J19" s="815" t="n">
-        <v>15.72</v>
+        <v>7.83</v>
       </c>
       <c r="K19" s="815" t="n">
-        <v>19.07</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="L19" s="815" t="n">
-        <v>21.11</v>
+        <v>8.65</v>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1" s="471">
@@ -24129,31 +24129,31 @@
       </c>
       <c r="C20" s="475" t="n"/>
       <c r="D20" s="816" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E20" s="816" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F20" s="816" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G20" s="816" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H20" s="816" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I20" s="800" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="J20" s="816" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="K20" s="816" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="L20" s="816" t="n">
         <v>1.54</v>
-      </c>
-      <c r="E20" s="816" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="F20" s="816" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="G20" s="816" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="H20" s="816" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="I20" s="800" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="J20" s="816" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="K20" s="816" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="L20" s="816" t="n">
-        <v>2.06</v>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1" s="471">
@@ -24164,31 +24164,31 @@
       </c>
       <c r="C21" s="475" t="n"/>
       <c r="D21" s="814" t="n">
-        <v>10801.74</v>
+        <v>13314.43</v>
       </c>
       <c r="E21" s="814" t="n">
-        <v>2566.37</v>
+        <v>3259.8</v>
       </c>
       <c r="F21" s="814" t="n">
-        <v>6940.88</v>
+        <v>8417.719999999999</v>
       </c>
       <c r="G21" s="814" t="n">
-        <v>7640.65</v>
+        <v>9279.42</v>
       </c>
       <c r="H21" s="814" t="n">
-        <v>8925.08</v>
+        <v>10946.07</v>
       </c>
       <c r="I21" s="805" t="n">
-        <v>10579.72</v>
+        <v>13042.44</v>
       </c>
       <c r="J21" s="814" t="n">
-        <v>12524.67</v>
+        <v>15410.43</v>
       </c>
       <c r="K21" s="814" t="n">
-        <v>14264.99</v>
+        <v>17707.09</v>
       </c>
       <c r="L21" s="814" t="n">
-        <v>15366.25</v>
+        <v>19091.63</v>
       </c>
     </row>
     <row r="24">
@@ -24257,7 +24257,7 @@
       <c r="E28" s="483" t="n"/>
       <c r="F28" s="475" t="n"/>
       <c r="G28" s="720" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="H28" s="483" t="n"/>
       <c r="I28" s="475" t="n"/>
@@ -24273,7 +24273,7 @@
       <c r="E29" s="483" t="n"/>
       <c r="F29" s="475" t="n"/>
       <c r="G29" s="720" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H29" s="483" t="n"/>
       <c r="I29" s="475" t="n"/>
@@ -24289,7 +24289,7 @@
       <c r="E30" s="483" t="n"/>
       <c r="F30" s="475" t="n"/>
       <c r="G30" s="718" t="n">
-        <v>1770.7</v>
+        <v>263.1</v>
       </c>
       <c r="H30" s="483" t="n"/>
       <c r="I30" s="475" t="n"/>
@@ -24305,7 +24305,7 @@
       <c r="E31" s="483" t="n"/>
       <c r="F31" s="475" t="n"/>
       <c r="G31" s="718" t="n">
-        <v>1930.1</v>
+        <v>398.8</v>
       </c>
       <c r="H31" s="483" t="n"/>
       <c r="I31" s="475" t="n"/>
@@ -24321,7 +24321,7 @@
       <c r="E32" s="483" t="n"/>
       <c r="F32" s="475" t="n"/>
       <c r="G32" s="718" t="n">
-        <v>2104.1</v>
+        <v>3509.8</v>
       </c>
       <c r="H32" s="483" t="n"/>
       <c r="I32" s="475" t="n"/>
@@ -24337,7 +24337,7 @@
       <c r="E33" s="483" t="n"/>
       <c r="F33" s="475" t="n"/>
       <c r="G33" s="777" t="n">
-        <v>1.542</v>
+        <v>1.441</v>
       </c>
       <c r="H33" s="483" t="n"/>
       <c r="I33" s="475" t="n"/>
@@ -24401,15 +24401,15 @@
       </c>
       <c r="C39" s="576" t="inlineStr">
         <is>
-          <t>528 − 956</t>
+          <t>2114 − 2453</t>
         </is>
       </c>
       <c r="D39" s="475" t="n"/>
       <c r="E39" s="432" t="n">
-        <v>45</v>
+        <v>242</v>
       </c>
       <c r="F39" s="815" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="G39" s="576" t="inlineStr">
         <is>
@@ -24425,19 +24425,19 @@
       </c>
       <c r="C40" s="576" t="inlineStr">
         <is>
-          <t>956 − 1384</t>
+          <t>2453 − 2791</t>
         </is>
       </c>
       <c r="D40" s="475" t="n"/>
       <c r="E40" s="432" t="n">
-        <v>458</v>
+        <v>3128</v>
       </c>
       <c r="F40" s="815" t="n">
-        <v>9.199999999999999</v>
+        <v>6.3</v>
       </c>
       <c r="G40" s="576" t="inlineStr">
         <is>
-          <t>█████████</t>
+          <t>███████</t>
         </is>
       </c>
       <c r="H40" s="483" t="n"/>
@@ -24449,19 +24449,19 @@
       </c>
       <c r="C41" s="576" t="inlineStr">
         <is>
-          <t>1384 − 1812</t>
+          <t>2791 − 3130</t>
         </is>
       </c>
       <c r="D41" s="475" t="n"/>
       <c r="E41" s="432" t="n">
-        <v>1120</v>
+        <v>8132</v>
       </c>
       <c r="F41" s="815" t="n">
-        <v>22.4</v>
+        <v>16.3</v>
       </c>
       <c r="G41" s="576" t="inlineStr">
         <is>
-          <t>██████████████████████</t>
+          <t>███████████████████</t>
         </is>
       </c>
       <c r="H41" s="483" t="n"/>
@@ -24473,15 +24473,15 @@
       </c>
       <c r="C42" s="576" t="inlineStr">
         <is>
-          <t>1812 − 2240</t>
+          <t>3130 − 3469</t>
         </is>
       </c>
       <c r="D42" s="475" t="n"/>
       <c r="E42" s="432" t="n">
-        <v>1474</v>
+        <v>12467</v>
       </c>
       <c r="F42" s="815" t="n">
-        <v>29.5</v>
+        <v>24.9</v>
       </c>
       <c r="G42" s="576" t="inlineStr">
         <is>
@@ -24497,19 +24497,19 @@
       </c>
       <c r="C43" s="604" t="inlineStr">
         <is>
-          <t>2240 − 2668</t>
+          <t>3469 − 3807</t>
         </is>
       </c>
       <c r="D43" s="475" t="n"/>
       <c r="E43" s="433" t="n">
-        <v>1107</v>
+        <v>12441</v>
       </c>
       <c r="F43" s="795" t="n">
-        <v>22.1</v>
+        <v>24.9</v>
       </c>
       <c r="G43" s="604" t="inlineStr">
         <is>
-          <t>██████████████████████</t>
+          <t>██████████████████████████████</t>
         </is>
       </c>
       <c r="H43" s="483" t="n"/>
@@ -24521,19 +24521,19 @@
       </c>
       <c r="C44" s="576" t="inlineStr">
         <is>
-          <t>2668 − 3096</t>
+          <t>3807 − 4146</t>
         </is>
       </c>
       <c r="D44" s="475" t="n"/>
       <c r="E44" s="432" t="n">
-        <v>522</v>
+        <v>8365</v>
       </c>
       <c r="F44" s="815" t="n">
-        <v>10.4</v>
+        <v>16.7</v>
       </c>
       <c r="G44" s="576" t="inlineStr">
         <is>
-          <t>██████████</t>
+          <t>████████████████████</t>
         </is>
       </c>
       <c r="H44" s="483" t="n"/>
@@ -24545,19 +24545,19 @@
       </c>
       <c r="C45" s="576" t="inlineStr">
         <is>
-          <t>3096 − 3524</t>
+          <t>4146 − 4485</t>
         </is>
       </c>
       <c r="D45" s="475" t="n"/>
       <c r="E45" s="432" t="n">
-        <v>200</v>
+        <v>3960</v>
       </c>
       <c r="F45" s="815" t="n">
-        <v>4</v>
+        <v>7.9</v>
       </c>
       <c r="G45" s="576" t="inlineStr">
         <is>
-          <t>████</t>
+          <t>█████████</t>
         </is>
       </c>
       <c r="H45" s="483" t="n"/>
@@ -24569,19 +24569,19 @@
       </c>
       <c r="C46" s="576" t="inlineStr">
         <is>
-          <t>3524 − 3952</t>
+          <t>4485 − 4823</t>
         </is>
       </c>
       <c r="D46" s="475" t="n"/>
       <c r="E46" s="432" t="n">
-        <v>58</v>
+        <v>1098</v>
       </c>
       <c r="F46" s="815" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="G46" s="576" t="inlineStr">
         <is>
-          <t>█</t>
+          <t>██</t>
         </is>
       </c>
       <c r="H46" s="483" t="n"/>
@@ -24593,15 +24593,15 @@
       </c>
       <c r="C47" s="576" t="inlineStr">
         <is>
-          <t>3952 − 4380</t>
+          <t>4823 − 5162</t>
         </is>
       </c>
       <c r="D47" s="475" t="n"/>
       <c r="E47" s="432" t="n">
-        <v>11</v>
+        <v>156</v>
       </c>
       <c r="F47" s="815" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="G47" s="576" t="inlineStr">
         <is>
@@ -24617,15 +24617,15 @@
       </c>
       <c r="C48" s="576" t="inlineStr">
         <is>
-          <t>4380 − 4808</t>
+          <t>5162 − 5501</t>
         </is>
       </c>
       <c r="D48" s="475" t="n"/>
       <c r="E48" s="432" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F48" s="815" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G48" s="576" t="inlineStr">
         <is>
@@ -24638,7 +24638,7 @@
     <row r="51" ht="43" customHeight="1" s="471">
       <c r="B51" s="553" t="inlineStr">
         <is>
-          <t>Симуляция: numpy seed=42, 50,000 итераций, 5 стохастических переменных (Revenue (Выручка) mult Triangular (Треугольное) 0.60–1.40, Margin shock N(0, 4%), CAPEX overrun LogN, Exit mult Tri 3–7×, Hit rate Binomial 12×0.70). Blend: 0.79+0.30×hr (centred at 1.0). IRR via numpy_financial.irr.</t>
+          <t>Симуляция: numpy seed=42, 50,000 итераций, 5 стохастических переменных (Revenue mult Triangular 0.60–1.40, Margin shock N(0, 4%), CAPEX overrun LogN σ=10%, Exit mult Tri 3–7×, Hit rate Binomial 12×0.70). Blend: 0.79+0.30×hr (centred at 1.0). IRR via numpy_financial.irr на CF [-1250,0,0,0,20%,50%,15%,15%].</t>
         </is>
       </c>
     </row>
@@ -37812,7 +37812,7 @@
       </c>
       <c r="E27" s="400" t="inlineStr">
         <is>
-          <t>IRR (внутренняя норма доходности) 20.09% · MOIC (мультипликатор вложенного капитала) 2.0× · Payback (Окупаемость) 3.23y · MC N=5 000: mean IRR (внутренняя норма доходности) 11.44%, P(&gt;hurdle (порог))=13.6%; A+C pattern (паттерн) 33/45/9/13 (см. дислеймер V.1-V.4)</t>
+          <t>IRR (внутренняя норма доходности) 20.09% · MOIC (мультипликатор вложенного капитала) 2.0× · Payback (Окупаемость) 3.23y · MC N=50,000: mean IRR (внутренняя норма доходности) 7.24%, P(IRR&gt;8%) = 19.4%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">

--- a/Investor_Package/investor_model_v1.0_Public.xlsx
+++ b/Investor_Package/investor_model_v1.0_Public.xlsx
@@ -15233,7 +15233,7 @@
         </is>
       </c>
       <c r="D140" s="94" t="n">
-        <v>2152</v>
+        <v>2167.4</v>
       </c>
       <c r="E140" s="522" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         </is>
       </c>
       <c r="D141" s="94" t="n">
-        <v>1689</v>
+        <v>1697.6</v>
       </c>
       <c r="E141" s="522" t="inlineStr">
         <is>
@@ -17841,16 +17841,16 @@
         <v>3</v>
       </c>
       <c r="F24" s="727" t="n">
-        <v>3</v>
+        <v>175</v>
       </c>
       <c r="G24" s="727" t="n">
-        <v>500</v>
+        <v>348</v>
       </c>
       <c r="H24" s="727" t="n">
         <v>520</v>
       </c>
       <c r="I24" s="754" t="n">
-        <v>1029</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="25">
@@ -17931,10 +17931,10 @@
         <v>3</v>
       </c>
       <c r="F27" s="727" t="n">
-        <v>3</v>
+        <v>175</v>
       </c>
       <c r="G27" s="727" t="n">
-        <v>500</v>
+        <v>348</v>
       </c>
       <c r="H27" s="727" t="n">
         <v>520</v>
@@ -23757,7 +23757,7 @@
     <row r="4" ht="52" customHeight="1" s="471">
       <c r="B4" s="540" t="inlineStr">
         <is>
-          <t>Распределения NDP (чистые распределяемые поступления), EBITDA (прибыль до вычетов), IRR (внутренняя норма доходности), MOIC (мультипликатор вложенного капитала), EV (стоимость предприятия) под Waterfall (Каскад) W₃ (DEFAULT (ПО УМОЛЧАНИЮ), 1× Liq Pref (Ликвидационная привилегия) + 8% coupon (купон) + 60/40). A+C asymmetric pattern (паттерн): Y2029=33%, Y2030=45%, Y2031=9%, Y2032=13% (frontload 78% в Y29-Y30). Percentiles, probability of hurdle (порог)/target pass, Value at Risk (Риск). Seed=42.</t>
+          <t>Распределения NDP (чистые распределяемые поступления), EBITDA (прибыль до вычетов), IRR (внутренняя норма доходности), MOIC (мультипликатор вложенного капитала), EV (стоимость предприятия) под Waterfall (Каскад) W₃ (DEFAULT (ПО УМОЛЧАНИЮ), 1× Liq Pref (Ликвидационная привилегия) + 8% coupon (купон) + 60/40). A+C asymmetric pattern (паттерн): Y4=20%, Y5=50%, Y6=15%, Y7=15% (simplified CF pattern) (frontload 78% в Y29-Y30). Percentiles, probability of hurdle (порог)/target pass, Value at Risk (Риск). Seed=42.</t>
         </is>
       </c>
     </row>
@@ -37822,7 +37822,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Base (Базовый) W₃ = hurdle (порог) 18% ровно</t>
+          <t>Base (Базовый) W₃ = 20.09%, hurdle (порог) 18% + 2.09pp</t>
         </is>
       </c>
     </row>
@@ -37905,7 +37905,7 @@
     <row r="35" ht="32" customHeight="1" s="471">
       <c r="B35" s="620" t="inlineStr">
         <is>
-          <t>Медиана Comps (EV (стоимость предприятия)/EBITDA (прибыль до вычетов) 8.9×)</t>
+          <t>Медиана Comps (EV (стоимость предприятия)/EBITDA (прибыль до вычетов) 5.71×)</t>
         </is>
       </c>
       <c r="C35" s="483" t="n"/>
@@ -38746,7 +38746,7 @@
     <row r="81" ht="170" customHeight="1" s="471">
       <c r="B81" s="634" t="inlineStr">
         <is>
-          <t>РЕКОМЕНДАЦИЯ: УТВЕРДИТЬ инвестицию T₁ = 1 250 млн ₽ в 4 транша с привязкой к milestone-ам (Dev gate 2026Q1 — 250 млн ₽, Prod gate 2026Q3 — 350 млн ₽, Post-prod 2027Q1 — 350 млн ₽, Release (Релиз) 2027Q3 — 300 млн ₽). Waterfall (Каскад) DEFAULT (ПО УМОЛЧАНИЮ) = W₃ (1× Liq Pref (Ликвидационная привилегия) + 8% coupon (купон) + 60/40): Base (Базовый) IRR (внутренняя норма доходности) 18.04% = hurdle (порог) 18% ровно, MOIC (мультипликатор вложенного капитала) 2.00×, Payback (Окупаемость) 3.75 лет. Премиум-опция W₄ (1× Liq Pref + 12% preferred × 5y + 65/35): Base (Базовый) IRR (внутренняя норма доходности) 19.73%, MOIC (мультипликатор вложенного капитала) 2.12× — для LP (ограниченный партнёр), требующих enhanced downside protection. Выбор W₃ vs W₄ — предмет переговоров; W₃ default (по умолчанию) предлагается как balanced базовый сценарий для broad LP audience.</t>
+          <t>РЕКОМЕНДАЦИЯ: УТВЕРДИТЬ инвестицию T₁ = 1 250 млн ₽ в 4 транша с привязкой к milestone-ам (Dev gate 2026Q1 — 250 млн ₽, Prod gate 2026Q3 — 350 млн ₽, Post-prod 2027Q1 — 350 млн ₽, Release (Релиз) 2027Q3 — 300 млн ₽). Waterfall (Каскад) DEFAULT (ПО УМОЛЧАНИЮ) = W₃ (1× Liq Pref (Ликвидационная привилегия) + 8% coupon (купон) + 60/40): Base (Базовый) IRR (внутренняя норма доходности) 20.09% = hurdle (порог) 18% ровно, MOIC (мультипликатор вложенного капитала) 2.00×, Payback (Окупаемость) 3.23 лет. Премиум-опция W₄ (1× Liq Pref + 12% preferred × 5y + 65/35): Base (Базовый) IRR (внутренняя норма доходности) 19.73%, MOIC (мультипликатор вложенного капитала) 2.12× — для LP (ограниченный партнёр), требующих enhanced downside protection. Выбор W₃ vs W₄ — предмет переговоров; W₃ default (по умолчанию) предлагается как balanced базовый сценарий для broad LP audience.</t>
         </is>
       </c>
     </row>
@@ -43828,11 +43828,11 @@
     <mergeCell ref="D42:N42"/>
     <mergeCell ref="B44:N44"/>
     <mergeCell ref="D38:N38"/>
-    <mergeCell ref="B19:N19"/>
+    <mergeCell ref="D23:N23"/>
     <mergeCell ref="D89:N89"/>
     <mergeCell ref="D29:N29"/>
     <mergeCell ref="B87:N87"/>
-    <mergeCell ref="D23:N23"/>
+    <mergeCell ref="B19:N19"/>
     <mergeCell ref="D54:N54"/>
     <mergeCell ref="B34:N34"/>
     <mergeCell ref="D14:N14"/>
@@ -47772,11 +47772,11 @@
 • Horizon 2026–2028 (3 года основного периода) + tail (хвостовой период) 2029–2032
 • 12 премиальных фильмов со средним бюджетом 154 млн ₽
 • Совокупная выручка 4 545 млн ₽ (Base (Базовый) сценарий)
-• GAAP (стандарты бухучёта) EBITDA (прибыль до вычетов) 2 152 млн ₽ (margin (маржа) 47.3% — 2.4× отраслевой медианы РФ)
-• Net Profit (Чистая прибыль) 1 689 млн ₽ после налогов (эффективная нагрузка 12.9%)
+• GAAP (стандарты бухучёта) EBITDA (прибыль до вычетов) 2 167 млн ₽ (margin (маржа) 47.3% — 2.4× отраслевой медианы РФ)
+• Net Profit (Чистая прибыль) 1 698 млн ₽ после налогов (эффективная нагрузка 12.9%)
 • Expected exit EV (стоимость предприятия) 6 038 млн ₽ на 2030 (probability-weighted)
-• MoIC ≈ 4.8× / IRR (внутренняя норма доходности) 38%+ при Base (Базовый) сценарии
-• Payback (Окупаемость) &lt; 24 месяцев</t>
+• MoIC (мультипликатор вложенного капитала) 2.0× / IRR (внутренняя норма доходности) 20.09% при Base (Базовый) W₃
+• Payback (Окупаемость) 3.2 года</t>
         </is>
       </c>
     </row>

--- a/Investor_Package/investor_model_v1.0_Public.xlsx
+++ b/Investor_Package/investor_model_v1.0_Public.xlsx
@@ -17591,7 +17591,7 @@
     <row r="4">
       <c r="B4" s="540" t="inlineStr">
         <is>
-          <t>WACC (средневзвешенная стоимость капитала) = 19.1% · Terminal growth (Терминальный рост) g = 3% · Exit Mult = 5.0× EBITDA (прибыль до вычетов)</t>
+          <t>WACC (средневзвешенная стоимость капитала) = 19.05% · Terminal growth (Терминальный рост) g = 3% · Exit Mult = 5.0× EBITDA (прибыль до вычетов)</t>
         </is>
       </c>
     </row>
@@ -18041,7 +18041,7 @@
       </c>
       <c r="C31" s="567" t="inlineStr">
         <is>
-          <t>PV FCFF (свободный денежный поток фирмы) @ WACC (средневзвешенная стоимость капитала) 19.1%</t>
+          <t>PV FCFF (свободный денежный поток фирмы) @ WACC (средневзвешенная стоимость капитала) 19.05%</t>
         </is>
       </c>
       <c r="D31" s="750" t="n">
@@ -18374,7 +18374,7 @@
     <row r="52">
       <c r="C52" s="574" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>19.05%</t>
         </is>
       </c>
       <c r="D52" s="727" t="n">
@@ -23951,7 +23951,7 @@
       </c>
       <c r="H12" s="543" t="inlineStr">
         <is>
-          <t>p=0,70, 12 films (фильмов)</t>
+          <t>p=0.70, 12 films (фильмов), σ=0.20 (beta uncertainty)</t>
         </is>
       </c>
       <c r="I12" s="475" t="n"/>
